--- a/AAII_Financials/Quarterly/GPN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GPN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>GPN</t>
   </si>
@@ -656,544 +656,557 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3320800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2969700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1932800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2007600</v>
       </c>
-      <c r="G8" s="3">
-        <v>1956700</v>
-      </c>
       <c r="H8" s="3">
+        <v>1969300</v>
+      </c>
+      <c r="I8" s="3">
         <v>1820300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1933200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1997700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1971000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1834100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2433800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2475700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2452500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2292400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2253000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2285400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2280900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2156300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2194000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2202300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2137400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1990000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1930200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1917800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1672000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1903600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1987800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1105900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>935200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>883000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>880600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>857700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>833200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>795000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1054300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1038900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>962200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>919800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>321600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>941800</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1293900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1273600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>563700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>556700</v>
       </c>
-      <c r="G9" s="3">
-        <v>498800</v>
-      </c>
       <c r="H9" s="3">
+        <v>501800</v>
+      </c>
+      <c r="I9" s="3">
         <v>495200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>519800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>504600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>504500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>499100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>902300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>915500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>942000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>947800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>927900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>931200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>962300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>957200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>968000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>944200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>936300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>925200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>922200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>900900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>893700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>933900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1029100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>424700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>301100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>304000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>313100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>265000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>264500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>252400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>509100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>493900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>469100</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>455900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>163600</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>468400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2026900</v>
+      </c>
+      <c r="E10" s="3">
         <v>1696100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1369100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1451000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1458000</v>
-      </c>
       <c r="H10" s="3">
+        <v>1467500</v>
+      </c>
+      <c r="I10" s="3">
         <v>1325100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1413400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1493100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1466600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1335000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1531500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1560200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1510500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1344700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1325100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1354200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1318600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1199100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1226000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1258100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1201100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1064800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1008000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1016900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>778300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>969700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>958700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>681200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>634100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>579000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>567500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>592700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>568700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>542600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>545200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>545000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>493100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>463900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>158000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>473400</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1236,8 +1249,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1256,11 +1270,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>55800</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1358,8 +1372,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1480,88 +1497,91 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>197800</v>
+      </c>
+      <c r="E14" s="3">
         <v>387300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>360600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-138800</v>
       </c>
-      <c r="G14" s="3">
-        <v>133400</v>
-      </c>
       <c r="H14" s="3">
+        <v>166700</v>
+      </c>
+      <c r="I14" s="3">
         <v>90700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-195400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>198300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>53600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>77800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>113600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>75100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-38200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>346200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>69800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>122200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1047100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>51000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>98600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>71600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>78300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>91800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>105900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>59800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>82200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>71600</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1572,21 +1592,21 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>21500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>8200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>18300</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
@@ -1602,53 +1622,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>884100</v>
+      </c>
+      <c r="E15" s="3">
         <v>864800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>341600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>303200</v>
       </c>
-      <c r="G15" s="3">
-        <v>132800</v>
-      </c>
       <c r="H15" s="3">
+        <v>297200</v>
+      </c>
+      <c r="I15" s="3">
         <v>292600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>304900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>310400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>140800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>461100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>448600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>458600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>462200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>407300</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1724,8 +1747,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1765,252 +1791,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2785900</v>
+      </c>
+      <c r="E17" s="3">
         <v>2598000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1394000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1368400</v>
       </c>
-      <c r="G17" s="3">
-        <v>1396100</v>
-      </c>
       <c r="H17" s="3">
+        <v>1409300</v>
+      </c>
+      <c r="I17" s="3">
         <v>1357700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1431900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1337800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1442000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1396700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1821400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1842400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1888000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1889500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1845400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1898900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2810800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1780300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1873000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1802300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1774900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1714700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1678200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1627400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1564400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1659600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1791600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>931900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>713400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>683500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>713600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>634500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>642400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>638800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>904700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>866400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>830400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>814800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>310000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>836600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>534900</v>
+      </c>
+      <c r="E18" s="3">
         <v>371700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>538800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>639200</v>
       </c>
-      <c r="G18" s="3">
-        <v>560600</v>
-      </c>
       <c r="H18" s="3">
+        <v>560000</v>
+      </c>
+      <c r="I18" s="3">
         <v>462700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>501300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>659900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>529000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>437400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>612400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>633300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>564500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>403000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>407600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>386500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-529900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>376000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>321000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>400000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>362500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>275300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>252000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>290400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>107600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>244000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>196200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>174000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>221800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>199500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>167000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>223200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>190800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>156200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>149600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>172500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>131800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>105000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>11600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2053,618 +2086,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-25000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-81600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-11600</v>
       </c>
-      <c r="G20" s="3">
-        <v>-30100</v>
-      </c>
       <c r="H20" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-29000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-33100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-26200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-33200</v>
       </c>
       <c r="L20" s="3">
         <v>-33200</v>
       </c>
       <c r="M20" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="N20" s="3">
         <v>-27000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-29200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-11100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>17600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>6500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>29100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>11100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>6000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>11600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>2400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>1900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>1600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1442900</v>
+      </c>
+      <c r="E21" s="3">
         <v>1261400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>962000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>954000</v>
       </c>
-      <c r="G21" s="3">
-        <v>723600</v>
-      </c>
       <c r="H21" s="3">
+        <v>887300</v>
+      </c>
+      <c r="I21" s="3">
         <v>784300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>839300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>996500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>703000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>931800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1088000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1121200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1037800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>825500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>813300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>809600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-101400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>802300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>746800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>825100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>788500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>703100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>664700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>726400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>511300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>632800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>604200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>368900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>372900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>347400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>323200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>350000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>317300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>289500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>273600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>288500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>241000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>215600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>47800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>215300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>261100</v>
+      </c>
+      <c r="E22" s="3">
         <v>239200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>196200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>141700</v>
       </c>
-      <c r="G22" s="3">
-        <v>151100</v>
-      </c>
       <c r="H22" s="3">
+        <v>151400</v>
+      </c>
+      <c r="I22" s="3">
         <v>144800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>152900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>146800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>151000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>157700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>165200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>173300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>172300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>119000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>118200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>132400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>97100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>89300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>85100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>82300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>79000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>81200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>82500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>82100</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>81100</v>
       </c>
       <c r="AB22" s="3">
         <v>81100</v>
       </c>
       <c r="AC22" s="3">
+        <v>81100</v>
+      </c>
+      <c r="AD22" s="3">
         <v>80200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>96000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>65500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>55400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>55500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>46000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>48100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>45500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>44400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>40800</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>48400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>41300</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>13500</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>52400</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-204700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>89000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>672600</v>
       </c>
-      <c r="G23" s="3">
-        <v>330400</v>
-      </c>
       <c r="H23" s="3">
+        <v>296300</v>
+      </c>
+      <c r="I23" s="3">
         <v>279700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>600500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>363800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>379700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>256600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>381700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>435500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>456400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-35800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>294400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>271600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-626100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>284400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>236500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>324200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>287500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>196400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>175200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>237400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>27500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>153800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>123200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>89100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>162300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>143300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>114400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>179900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>145600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>122300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>108000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>134100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>85300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>65300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>54200</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-11800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-111000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>199300</v>
       </c>
-      <c r="G24" s="3">
-        <v>118300</v>
-      </c>
       <c r="H24" s="3">
+        <v>40900</v>
+      </c>
+      <c r="I24" s="3">
         <v>43800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>110300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>59900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>64700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>58900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>172200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>47400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>52800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>52200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>37400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>50100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>60800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>20700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>18000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>42800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>15500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>22400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>32200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>24100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>54300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>27900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>24700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>16400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>15700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>12900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>12300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>6100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2785,252 +2834,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>130900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-192800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>200000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>473300</v>
       </c>
-      <c r="G26" s="3">
-        <v>212100</v>
-      </c>
       <c r="H26" s="3">
+        <v>255400</v>
+      </c>
+      <c r="I26" s="3">
         <v>235900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>490200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>303900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>315000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>249900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>372400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>376600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>284200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>247000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>257400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-678900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>232200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>199100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>274100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>226600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>175700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>157200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>194600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>26700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>138300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>100800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>105700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>130000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>119200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>60000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>186000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>117700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>97600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>91600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>118400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>72400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>53000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-7400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>52600</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1799900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>217500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>635200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>241600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>305700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>567200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>315100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>374800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>313300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>361300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>361800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>274100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>249300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>290500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-673000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>244700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>208500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>296700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>263600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>196700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>182600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>221000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>37300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>143600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>102800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>95000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>120500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>112300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>51900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>176400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>109100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>91400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>83300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>110700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>66900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>48800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-9600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3151,41 +3209,44 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-102000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-1586200</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>36600</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>187300</v>
       </c>
-      <c r="G29" s="3">
-        <v>34000</v>
-      </c>
       <c r="H29" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="I29" s="3">
         <v>76800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>108100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>29700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>74300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>73100</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -3225,8 +3286,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3243,11 +3304,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>23300</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3255,11 +3316,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>158700</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3273,8 +3334,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3395,8 +3459,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3517,252 +3584,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E32" s="3">
         <v>25000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>81600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>11600</v>
       </c>
-      <c r="G32" s="3">
-        <v>30100</v>
-      </c>
       <c r="H32" s="3">
+        <v>30200</v>
+      </c>
+      <c r="I32" s="3">
         <v>29000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>33100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>26200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>33200</v>
       </c>
       <c r="L32" s="3">
         <v>33200</v>
       </c>
       <c r="M32" s="3">
+        <v>33200</v>
+      </c>
+      <c r="N32" s="3">
         <v>27000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>29200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>11100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>15300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-17600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-6500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-29100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>9000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-11100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-11600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1799900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>217500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>635200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>241600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>305700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>567200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>315100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>374800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>313300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>361300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>361800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>274100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>249300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>290500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-673000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>244700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>208500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>296700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>263600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>196700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>182600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>221000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>37300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>143600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>102800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>95000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>120500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>112300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>75200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>176400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>109100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>91400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>242000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>110700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>66900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>48800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-9600</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3883,257 +3959,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1799900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>217500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>635200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>241600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>305700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>567200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>315100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>374800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>313300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>361300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>361800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>274100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>249300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>290500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-673000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>244700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>208500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>296700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>263600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>196700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>182600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>221000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>37300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>143600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>102800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>95000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>120500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>112300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>75200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>176400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>109100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>91400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>242000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>110700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>66900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>48800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-9600</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4176,8 +4261,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4220,130 +4306,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5409000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5861300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8336400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2603000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2611700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2896000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2356500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2941900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2097200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2167600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2088900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1941800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1919600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2001700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1997600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1993800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1933300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2045300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1979300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2347700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1799500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2082400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1945900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2220800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1825600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1800100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1678300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2127600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1047700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1277600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1210900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>990600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1099500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1005800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1335900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1186100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1080600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1261800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1162800</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>995800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4464,130 +4554,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1577000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1415700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>784200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>878200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>864400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1112300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>787700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1150800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1134300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1054200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1120100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1077900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1159300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1067200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3847200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3059500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2846000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2729700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2381700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3095100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2697300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2479400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2278800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2450800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2340000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2078100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2249000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2424400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3238900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3157000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1948600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3215900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2351200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2938200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2761200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2143600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1288100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1023500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1830100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1392700</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4630,8 +4726,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4708,263 +4804,272 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3619300</v>
+      </c>
+      <c r="E45" s="3">
         <v>3353300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2680100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3313800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3871600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1836900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2337000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3020900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4496800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5617600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4097400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2973100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1608000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1738800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>469400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>437700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>377400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>350000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>349500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>403000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>317000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>367700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>297000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>185700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>191500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>439200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>440500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>261100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>235100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>216700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>207500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>208300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>213800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>206500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>220600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>147400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>113800</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>123100</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>186500</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11669800</v>
+      </c>
+      <c r="E46" s="3">
         <v>11674200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12602700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7206900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7753000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6738600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6031200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7901100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8550300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9669900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8073800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6780300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5519100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5595100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6314100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5453400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5217000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5152400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4711000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5792300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4899900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4878800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4592400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4968700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4351300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4069700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4366400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4992600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4547700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4669800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3376200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4414000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3658900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4157900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4303600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3550300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2516100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2399200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3116000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2575000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>1024400</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
@@ -4972,23 +5077,23 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>987200</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1600</v>
       </c>
-      <c r="L47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>989600</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
@@ -4996,41 +5101,41 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>152500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>139800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>131600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>123900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>113400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>106200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>99600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>91100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>335200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>72100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>62500</v>
-      </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC47" s="3" t="s">
         <v>8</v>
@@ -5044,8 +5149,8 @@
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG47" s="3">
-        <v>0</v>
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH47" s="3">
         <v>0</v>
@@ -5074,252 +5179,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2134800</v>
+      </c>
+      <c r="E48" s="3">
         <v>2012200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1752100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1440400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1414200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2352700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1668800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2334600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2309300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2200400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2535700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2118000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2084200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2023500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1838800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1759200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1689300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1716300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1687600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1667300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1642300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1580700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1578500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1526200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1477600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1441900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1819600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1879300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>931400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>899500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>653500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>641000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>615800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>599800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>588300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>577200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>537900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>552000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>526400</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>520700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>46394700</v>
+      </c>
+      <c r="E49" s="3">
         <v>47258400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>21307900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>21011200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>21122900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>35085200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>21641700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>36278100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>36467800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>36525000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>36911600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>36776800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>37233200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>37438600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>32979100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>33328900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>33769200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>36086000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>36447000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>35874100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>36237100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>35552700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>35887300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>35997000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>36218500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>36477200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>36914400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>36938800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>8653900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8751300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8830000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8409900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7669200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7811200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7885700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>7945100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>6817200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>6856800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>6892900</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>6939600</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5440,8 +5554,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5562,130 +5679,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1827600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1809400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15286500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17093600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16917900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2017200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15251100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2023600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2005600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1981600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>451700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1927400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1940700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3002000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3524400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3257500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3368800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2356700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2320800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2314500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2270800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2154400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1808200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1985800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1891400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1860900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1379700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1401400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>451100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>429000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>371100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>374400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>355900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>334400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>220400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>208900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>165600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>151800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>129100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>77800</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5806,130 +5929,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>63573800</v>
+      </c>
+      <c r="E54" s="3">
         <v>64254800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>53338500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>47962400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48518500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>47616100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>46890300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>49985800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>50752200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>51774800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>50570200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>48924600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>48150900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>48638600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>44809000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>43938700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>44175800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>45435300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>45279700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>45754500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>45149700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>44257700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>44201500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>44549800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>44001500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>43849600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>44480200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>45212000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>14584100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>14749600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>13230800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>13839200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12299900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12903300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12998100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>12281500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>10036800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>9959700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>10664400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>10113100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5972,8 +6101,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6016,344 +6146,351 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3514600</v>
+      </c>
+      <c r="E57" s="3">
         <v>3551000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>278100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2263700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2009100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2706100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>254300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2455200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2451700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2420100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>290400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2338300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2481100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2290900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4630100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3786200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3926800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4039700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3672500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4188200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3623100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3379800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3145100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2938100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2761800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2403500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2992200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3613900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3547100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3678600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2453100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3488500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2742300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3353800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3080100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2541500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1691200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1635500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2282100</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1564800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2061800</v>
+      </c>
+      <c r="E58" s="3">
         <v>2592600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2323900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2876600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2496200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1908400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1581600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2340900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2575100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2675300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1683500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>790500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>604700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1667700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1916400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1598800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1749300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>617600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>562700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>627500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>540100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>523900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1186100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1270900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1272800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>445700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>498400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>581000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>887300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>774900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>815600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>778600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>622100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>555100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>735500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>580900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>404800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>455400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>569900</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>645100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8577400</v>
+      </c>
+      <c r="E59" s="3">
         <v>8603300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3936700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3292700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3678100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2526400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3583800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3698700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4302600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5420600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5244100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3093900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2032700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2124800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>352100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>291700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>305800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>209900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>227800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>218600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>216300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>212500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>217900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>206300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>194700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>187100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>88800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>88300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>49200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>62700</v>
-      </c>
-      <c r="AG59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH59" s="3" t="s">
         <v>8</v>
@@ -6367,389 +6504,401 @@
       <c r="AK59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AL59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM59" s="3">
         <v>1500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1900</v>
-      </c>
-      <c r="AO59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AP59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14153800</v>
+      </c>
+      <c r="E60" s="3">
         <v>14747000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7456800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8433000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8183400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7140900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6252700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8528900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9329400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10516000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8125700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6222700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5118400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6083400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6898700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5676700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5981800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4867200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4463000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5034300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4379600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4116200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4549100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4415300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4229300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3036300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3579300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4283200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4483600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4516200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3268600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4267100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3364400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3908900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3815600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3123900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2098500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2092900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2852000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2209900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>21494000</v>
+      </c>
+      <c r="E61" s="3">
         <v>20994600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19866200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>13383500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14171800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15031800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15417400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15250000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15611900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15569000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>16131700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>16570800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16983900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16580500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12289200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12289800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10883700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11723800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>11414800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10709800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10217000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9627100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8466400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8437000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8440300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9636100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9090400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8987700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5000600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5170400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5015200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4707500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4255100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>4176900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4559400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>4677900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>4175400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>4221300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>4260800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>4316400</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1047800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1079500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>610800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>938400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1017000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>598300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>597800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>576500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>581800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>585700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>228900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>620000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>630800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>607500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3080900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3099300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3333800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3449500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3532500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3656000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3702900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3672300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3699000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3733700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3698900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3656800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3755500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3985500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>924800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>920600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>760600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>689100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>664400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>677700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>657800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>784800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>758300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>769300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>772200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>785000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6870,8 +7019,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6992,8 +7144,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7114,130 +7269,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>39604100</v>
+      </c>
+      <c r="E66" s="3">
         <v>39580300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>29559000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24464600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25096900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24591500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23873700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26366200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27591100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28788600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26782700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25766700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>25235400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25755800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22505500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>21278200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20420200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>20275700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19651500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19607400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18455900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17566000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16869200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16804100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16575600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16528800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16624400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17437400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>10593500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10798800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9239400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9865000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>8469500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>8951700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>9203500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>8750200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>7185800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>7228800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>8033600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>7457500</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7280,8 +7441,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7402,8 +7564,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7524,8 +7689,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7646,8 +7814,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7768,130 +7939,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4014700</v>
+      </c>
+      <c r="E72" s="3">
         <v>4068200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5936300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5777900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5200600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5019300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4774700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4269900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4018200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3706900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3457200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3160700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2863900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2654600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2731400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2547900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2326300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3068700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2982100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2845200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2664700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2500800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2570900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2477000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2314400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2335400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2333000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2297900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2204400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2111800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2066400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1994000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1819200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1738500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1597900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1357500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1255600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1192500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1137200</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1146800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8012,8 +8189,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8134,8 +8314,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8256,130 +8439,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23110700</v>
+      </c>
+      <c r="E76" s="3">
         <v>23792400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22888800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22668100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22593100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22248300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22280700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22811400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22387400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22215800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22999200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22441500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22171500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22083300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22303500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22660600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>23755700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>25159600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>25628200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>26147000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>26693800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>26691800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>27332400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>27745700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>27425900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>27320800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>27855700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>27774600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3990600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3950800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3991400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3974300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3830400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3951600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3794500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3531300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>2851000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2730900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2630800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>2655600</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8500,257 +8689,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42704</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1799900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>217500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>635200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>241600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>305700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>567200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>315100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>374800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>313300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>361300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>361800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>274100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>249300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>290500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-673000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>244700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>208500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>296700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>263600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>196700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>182600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>221000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>37300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>143600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>102800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>95000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>120500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>112300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>75200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>176400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>109100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>91400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>242000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>110700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>66900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>48800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-9600</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8793,130 +8991,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>96500</v>
+      </c>
+      <c r="E83" s="3">
         <v>95400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>97500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>96600</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="H83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>117900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>116100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>118300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>117800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>106000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>100100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>99500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>100200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>99700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>400700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>405500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>427600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>428700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>425200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>418600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>422000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>425600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>407000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>406900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>402700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>397800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>400800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>183700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>145100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>148600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>153400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>124100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>123600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>121700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>121200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>113600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>107300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>109000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>35700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>108700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9037,8 +9239,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9159,8 +9364,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9281,8 +9489,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9403,8 +9614,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9525,130 +9739,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>662600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-288800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>515200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>768700</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="H89" s="3">
+        <v>817500</v>
+      </c>
+      <c r="I89" s="3">
+        <v>555100</v>
+      </c>
+      <c r="J89" s="3">
+        <v>883400</v>
+      </c>
+      <c r="K89" s="3">
+        <v>835700</v>
+      </c>
+      <c r="L89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H89" s="3">
-        <v>555100</v>
-      </c>
-      <c r="I89" s="3">
-        <v>883400</v>
-      </c>
-      <c r="J89" s="3">
-        <v>835700</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>529600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>657500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>426800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>565000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>599500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>709500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>336400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>568100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>630000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>753200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>918000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>510200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>599400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>769400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>584500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>523700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>436600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>41900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1102000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>17600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>229700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>445100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>154300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>222200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>284500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>152300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>92100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-25900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>294000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>309300</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>37900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9691,130 +9911,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-235700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-261300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-168200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-169800</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="H91" s="3">
+        <v>-152200</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-127600</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-184000</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-166300</v>
+      </c>
+      <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H91" s="3">
-        <v>-127600</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-184000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-166300</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-145400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-157300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-169800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-168800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-162200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-152300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-139300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-167900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-156100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-142500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-131200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-133400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-86200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-106800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-121000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-103600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-104800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-106900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-67700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-78200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-55100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-57200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-53400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-58900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-43800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-45300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-46700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-43700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-46200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-5600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-41900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9935,8 +10159,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10057,130 +10284,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-263500</v>
+      </c>
+      <c r="E94" s="3">
         <v>5716100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-309900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>556400</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="H94" s="3">
+        <v>-303700</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-173100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>672700</v>
+      </c>
+      <c r="K94" s="3">
+        <v>-149300</v>
+      </c>
+      <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H94" s="3">
-        <v>-173100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>672700</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-149300</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-148000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-241400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-118100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>205300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4206800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-188600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-123200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-202900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-160800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-998000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-133900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1065000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-96900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-43300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-124700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-169700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-410800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-307900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-82100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-116300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-548800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-823400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-58700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-45400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-623500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-40100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-46600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-5900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-42600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10223,91 +10456,92 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>66500</v>
+      </c>
+      <c r="E96" s="3">
         <v>68200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>59100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>58000</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="H96" s="3">
+        <v>60400</v>
+      </c>
+      <c r="I96" s="3">
+        <v>61100</v>
+      </c>
+      <c r="J96" s="3">
+        <v>62300</v>
+      </c>
+      <c r="K96" s="3">
+        <v>63400</v>
+      </c>
+      <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H96" s="3">
-        <v>61100</v>
-      </c>
-      <c r="I96" s="3">
-        <v>62300</v>
-      </c>
-      <c r="J96" s="3">
-        <v>63400</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>63600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>64800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>65000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>64900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>65800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-65900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-68800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-69100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-70200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-71500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-73300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-57300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-57600</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>116600</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-58300</v>
       </c>
       <c r="AB96" s="3">
         <v>-58300</v>
       </c>
       <c r="AC96" s="3">
+        <v>-58300</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-18500</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-1600</v>
       </c>
       <c r="AE96" s="3">
         <v>-1600</v>
@@ -10334,19 +10568,22 @@
         <v>-1600</v>
       </c>
       <c r="AM96" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1500</v>
       </c>
-      <c r="AO96" s="3">
-        <v>0</v>
-      </c>
       <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10467,8 +10704,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10589,8 +10829,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10711,370 +10954,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-833800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8410500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5858500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1603700</v>
       </c>
-      <c r="G100" s="3" t="s">
+      <c r="H100" s="3">
+        <v>-490700</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-1845800</v>
+      </c>
+      <c r="K100" s="3">
+        <v>111200</v>
+      </c>
+      <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H100" s="3">
-        <v>-31500</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-1845800</v>
-      </c>
-      <c r="J100" s="3">
-        <v>111200</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-276700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-317300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-242900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-909600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3610800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-572100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-61900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-366300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-376300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-95200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-218400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>277300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-369000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-951500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-84500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-432600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-77500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-138600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>322400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-163300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-49200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>336000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>564700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-41800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-572000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>19200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>624100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-131000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-160000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-135100</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>44400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>168600</v>
+      </c>
+      <c r="E101" s="3">
         <v>61800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-113900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>54700</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-34000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>48200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-70300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>16000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>18600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>109300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-93600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-78800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>109300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-93600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-78800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-36100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-36700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>15200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-21100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>94400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>20000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>35100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-67700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>58100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-36700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>2700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>4200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>12800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>15700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>11700</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-21700</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-431600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2991900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6079800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-303300</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>191600</v>
+      </c>
+      <c r="I102" s="3">
         <v>412300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-403500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>852400</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>70800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>147000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-123400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>22100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>58100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>57700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-79900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>56700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-345600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>528900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-262400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>112300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-131100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>395200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>25600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>121800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-449300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1079900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-229900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>66800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>220300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-108900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>93700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-330000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>149800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>105500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-181300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>99100</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>167000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>18000</v>
       </c>
     </row>
